--- a/data/metabolomics/metabolite_manual_annotations.xlsx
+++ b/data/metabolomics/metabolite_manual_annotations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tacaro/Documents/GitHub/DroughtSIP/data/metabolomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AE70D31-6A06-A04A-B474-07763090CD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5346A57D-BF70-8443-9C4E-7492D902EF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1820" windowWidth="27240" windowHeight="16440" xr2:uid="{A4A94BAB-C50F-CF46-BBED-298BF0D81361}"/>
+    <workbookView xWindow="30240" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{A4A94BAB-C50F-CF46-BBED-298BF0D81361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="438">
   <si>
     <t>compound</t>
   </si>
@@ -575,12 +575,6 @@
     <t>aspartic acid</t>
   </si>
   <si>
-    <t>azelaic acid (GCMS)</t>
-  </si>
-  <si>
-    <t>azelaic acid (LCMS)</t>
-  </si>
-  <si>
     <t>behenic acid</t>
   </si>
   <si>
@@ -692,24 +686,6 @@
     <t>cysteine sulfonic acid</t>
   </si>
   <si>
-    <t>cytidine (GCMS)</t>
-  </si>
-  <si>
-    <t>cytidine (LCMS)</t>
-  </si>
-  <si>
-    <t>cytosine (GCMS)</t>
-  </si>
-  <si>
-    <t>cytosine (LCMS)</t>
-  </si>
-  <si>
-    <t>dehydroabietic acid (GCMS)</t>
-  </si>
-  <si>
-    <t>dehydroabietic acid (LCMS)</t>
-  </si>
-  <si>
     <t>deoxyguanosine</t>
   </si>
   <si>
@@ -752,21 +728,9 @@
     <t>ethanolamine</t>
   </si>
   <si>
-    <t>ferulic acid (GCMS)</t>
-  </si>
-  <si>
-    <t>ferulic acid (LCMS)</t>
-  </si>
-  <si>
     <t>ferulic acid 4-sulfate</t>
   </si>
   <si>
-    <t>fructose (GCMS)</t>
-  </si>
-  <si>
-    <t>fructose (LCMS)</t>
-  </si>
-  <si>
     <t>fucose</t>
   </si>
   <si>
@@ -806,12 +770,6 @@
     <t>gluconic acid lactone</t>
   </si>
   <si>
-    <t>glucose (GCMS)</t>
-  </si>
-  <si>
-    <t>glucose (LCMS)</t>
-  </si>
-  <si>
     <t>glutamic acid (GCMS)</t>
   </si>
   <si>
@@ -920,12 +878,6 @@
     <t>isobutylamine</t>
   </si>
   <si>
-    <t>isoleucine (GCMS)</t>
-  </si>
-  <si>
-    <t>isoleucine (LCMS)</t>
-  </si>
-  <si>
     <t>isomaltose</t>
   </si>
   <si>
@@ -941,33 +893,15 @@
     <t>lactobionic acid</t>
   </si>
   <si>
-    <t>lactose (GCMS)</t>
-  </si>
-  <si>
-    <t>lactose (LCMS)</t>
-  </si>
-  <si>
     <t>lactulose</t>
   </si>
   <si>
     <t>laurdan</t>
   </si>
   <si>
-    <t>leucine (GCMS)</t>
-  </si>
-  <si>
-    <t>leucine (LCMS)</t>
-  </si>
-  <si>
     <t>leucrose</t>
   </si>
   <si>
-    <t>levoglucosan (GCMS)</t>
-  </si>
-  <si>
-    <t>levoglucosan (LCMS)</t>
-  </si>
-  <si>
     <t>lignoceric acid</t>
   </si>
   <si>
@@ -1013,12 +947,6 @@
     <t>mandelic acid</t>
   </si>
   <si>
-    <t>mannitol (GCMS)</t>
-  </si>
-  <si>
-    <t>mannitol (LCMS)</t>
-  </si>
-  <si>
     <t>mannoheptulose</t>
   </si>
   <si>
@@ -1070,12 +998,6 @@
     <t>neomycin B</t>
   </si>
   <si>
-    <t>nicotinic acid (GCMS)</t>
-  </si>
-  <si>
-    <t>nicotinic acid (LCMS)</t>
-  </si>
-  <si>
     <t>nonadecanoic acid</t>
   </si>
   <si>
@@ -1097,12 +1019,6 @@
     <t>ornithine</t>
   </si>
   <si>
-    <t>orotic acid (GCMS)</t>
-  </si>
-  <si>
-    <t>orotic acid (LCMS)</t>
-  </si>
-  <si>
     <t>oxoproline</t>
   </si>
   <si>
@@ -1139,12 +1055,6 @@
     <t>perfluoroheptanoic acid</t>
   </si>
   <si>
-    <t>perseitol (GCMS)</t>
-  </si>
-  <si>
-    <t>perseitol (LCMS)</t>
-  </si>
-  <si>
     <t>phenol</t>
   </si>
   <si>
@@ -1154,24 +1064,12 @@
     <t>phenylacetic acid</t>
   </si>
   <si>
-    <t>phenylalanine (GCMS)</t>
-  </si>
-  <si>
-    <t>phenylalanine (LCMS)</t>
-  </si>
-  <si>
     <t>phenylethylamine</t>
   </si>
   <si>
     <t>phenylpyruvate</t>
   </si>
   <si>
-    <t>phosphate (GCMS)</t>
-  </si>
-  <si>
-    <t>phosphate (LCMS)</t>
-  </si>
-  <si>
     <t>pimelic acid</t>
   </si>
   <si>
@@ -1214,12 +1112,6 @@
     <t>quinolinic acid</t>
   </si>
   <si>
-    <t>raffinose (GCMS)</t>
-  </si>
-  <si>
-    <t>raffinose (LCMS)</t>
-  </si>
-  <si>
     <t>ribonic acid</t>
   </si>
   <si>
@@ -1247,12 +1139,6 @@
     <t>sebacic acid</t>
   </si>
   <si>
-    <t>serine (GCMS)</t>
-  </si>
-  <si>
-    <t>serine (LCMS)</t>
-  </si>
-  <si>
     <t>shikimic acid</t>
   </si>
   <si>
@@ -1271,27 +1157,9 @@
     <t>stigmasterol</t>
   </si>
   <si>
-    <t>suberic acid (GCMS)</t>
-  </si>
-  <si>
-    <t>suberic acid (LCMS)</t>
-  </si>
-  <si>
     <t>succinate semialdehyde</t>
   </si>
   <si>
-    <t>succinic acid (GCMS)</t>
-  </si>
-  <si>
-    <t>succinic acid (LCMS)</t>
-  </si>
-  <si>
-    <t>sucrose (GCMS)</t>
-  </si>
-  <si>
-    <t>sucrose (LCMS)</t>
-  </si>
-  <si>
     <t>sulfoacetic acid</t>
   </si>
   <si>
@@ -1325,12 +1193,6 @@
     <t>threonic acid</t>
   </si>
   <si>
-    <t>threonine (GCMS)</t>
-  </si>
-  <si>
-    <t>threonine (LCMS)</t>
-  </si>
-  <si>
     <t>threose</t>
   </si>
   <si>
@@ -1352,39 +1214,15 @@
     <t>trimethylamine</t>
   </si>
   <si>
-    <t>tryptophan (GCMS)</t>
-  </si>
-  <si>
-    <t>tryptophan (LCMS)</t>
-  </si>
-  <si>
     <t>tyramine</t>
   </si>
   <si>
-    <t>tyrosine (GCMS)</t>
-  </si>
-  <si>
-    <t>tyrosine (LCMS)</t>
-  </si>
-  <si>
     <t>undecanedioic acid</t>
   </si>
   <si>
-    <t>uracil (GCMS)</t>
-  </si>
-  <si>
-    <t>uracil (LCMS)</t>
-  </si>
-  <si>
     <t>urea</t>
   </si>
   <si>
-    <t>uric acid (GCMS)</t>
-  </si>
-  <si>
-    <t>uric acid (LCMS)</t>
-  </si>
-  <si>
     <t>uridine</t>
   </si>
   <si>
@@ -1400,12 +1238,6 @@
     <t>vanillic acid</t>
   </si>
   <si>
-    <t>xanthine (GCMS)</t>
-  </si>
-  <si>
-    <t>xanthine (LCMS)</t>
-  </si>
-  <si>
     <t>xanthosine</t>
   </si>
   <si>
@@ -1419,6 +1251,105 @@
   </si>
   <si>
     <t>xylulose</t>
+  </si>
+  <si>
+    <t>refs</t>
+  </si>
+  <si>
+    <t>Warren (2015) Burg &amp; Ferrais (2008)	Reuter et al. (2010)</t>
+  </si>
+  <si>
+    <t>Warren (2015) Burg &amp; Ferrais (2008)</t>
+  </si>
+  <si>
+    <t>Warren (2015)Reuter et al. (2010)</t>
+  </si>
+  <si>
+    <t>Warren (2015) Skjerdal et al. (1996)</t>
+  </si>
+  <si>
+    <t>raffinose</t>
+  </si>
+  <si>
+    <t>serine</t>
+  </si>
+  <si>
+    <t>suberic acid</t>
+  </si>
+  <si>
+    <t>succinic acid</t>
+  </si>
+  <si>
+    <t>sucrose</t>
+  </si>
+  <si>
+    <t>threonine</t>
+  </si>
+  <si>
+    <t>tryptophan</t>
+  </si>
+  <si>
+    <t>tyrosine</t>
+  </si>
+  <si>
+    <t>uracil</t>
+  </si>
+  <si>
+    <t>uric acid</t>
+  </si>
+  <si>
+    <t>xanthine</t>
+  </si>
+  <si>
+    <t>phosphate</t>
+  </si>
+  <si>
+    <t>phenylalanine</t>
+  </si>
+  <si>
+    <t>perseitol</t>
+  </si>
+  <si>
+    <t>orotic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicotinic acid </t>
+  </si>
+  <si>
+    <t>mannitol</t>
+  </si>
+  <si>
+    <t>levoglucosan</t>
+  </si>
+  <si>
+    <t>leucine</t>
+  </si>
+  <si>
+    <t>lactose</t>
+  </si>
+  <si>
+    <t>isoleucine</t>
+  </si>
+  <si>
+    <t>glucose</t>
+  </si>
+  <si>
+    <t>fructose</t>
+  </si>
+  <si>
+    <t>ferulic acid</t>
+  </si>
+  <si>
+    <t>dehydroabietic acid</t>
+  </si>
+  <si>
+    <t>cytosine</t>
+  </si>
+  <si>
+    <t>cytidine</t>
+  </si>
+  <si>
+    <t>azelaic acid</t>
   </si>
 </sst>
 </file>
@@ -1801,92 +1732,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C09BAD44-0606-874E-9D44-23B566EFC583}">
-  <dimension ref="A1:B458"/>
+  <dimension ref="A1:C430"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="91.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -2291,50 +2226,53 @@
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>98</v>
       </c>
       <c r="B98" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C98" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>106</v>
       </c>
@@ -2342,7 +2280,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>108</v>
       </c>
@@ -2350,7 +2288,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>109</v>
       </c>
@@ -2358,7 +2296,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>110</v>
       </c>
@@ -2366,7 +2304,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>111</v>
       </c>
@@ -2374,27 +2312,27 @@
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -2402,7 +2340,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -2410,7 +2348,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -2418,7 +2356,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>119</v>
       </c>
@@ -2426,7 +2364,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -2434,7 +2372,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -2442,7 +2380,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>122</v>
       </c>
@@ -2450,7 +2388,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>123</v>
       </c>
@@ -2458,7 +2396,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>124</v>
       </c>
@@ -2466,7 +2404,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>125</v>
       </c>
@@ -2474,7 +2412,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>126</v>
       </c>
@@ -2482,25 +2420,28 @@
         <v>107</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>129</v>
       </c>
       <c r="B127" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C127" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>130</v>
       </c>
@@ -2626,6 +2567,9 @@
       <c r="A150" t="s">
         <v>152</v>
       </c>
+      <c r="B150" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
@@ -2780,1481 +2724,1326 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>179</v>
+        <v>437</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>192</v>
+        <v>191</v>
+      </c>
+      <c r="B190" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>193</v>
-      </c>
-      <c r="B191" t="s">
-        <v>99</v>
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>217</v>
+        <v>436</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>218</v>
+        <v>435</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>219</v>
+        <v>434</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>225</v>
+      </c>
+      <c r="B227" t="s">
+        <v>99</v>
+      </c>
+      <c r="C227" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A225" t="s">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A226" t="s">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A227" t="s">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A228" t="s">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A229" t="s">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>432</v>
+      </c>
+      <c r="B234" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A230" t="s">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A231" t="s">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
         <v>233</v>
       </c>
-      <c r="B231" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A232" t="s">
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A233" t="s">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A234" t="s">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
         <v>236</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A235" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A236" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A237" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A238" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A239" t="s">
-        <v>241</v>
-      </c>
-      <c r="B239" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A240" t="s">
-        <v>242</v>
-      </c>
-      <c r="B240" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>250</v>
+        <v>431</v>
+      </c>
+      <c r="B248" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>256</v>
-      </c>
-      <c r="B254" t="s">
-        <v>107</v>
+        <v>249</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>257</v>
-      </c>
-      <c r="B255" t="s">
-        <v>107</v>
+        <v>250</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A273" t="s">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A274" t="s">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A275" t="s">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A276" t="s">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A277" t="s">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A278" t="s">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>430</v>
+      </c>
+      <c r="B285" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A279" t="s">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A280" t="s">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
         <v>282</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A281" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A282" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A283" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A284" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A285" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A286" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A287" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A288" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>293</v>
+        <v>429</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>294</v>
-      </c>
-      <c r="B292" t="s">
-        <v>107</v>
+        <v>285</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>295</v>
-      </c>
-      <c r="B293" t="s">
-        <v>107</v>
+        <v>286</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>296</v>
+        <v>428</v>
+      </c>
+      <c r="B294" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>298</v>
+        <v>427</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>305</v>
-      </c>
-      <c r="B303" t="s">
-        <v>107</v>
+        <v>294</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312" t="s">
+        <v>426</v>
+      </c>
+      <c r="B312" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" t="s">
         <v>306</v>
       </c>
-      <c r="B304" t="s">
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" t="s">
+        <v>308</v>
+      </c>
+      <c r="B318" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A305" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A306" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A307" t="s">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A308" t="s">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" t="s">
         <v>310</v>
-      </c>
-    </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A309" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A310" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A311" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A312" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A313" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A314" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A315" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A316" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A317" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A318" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A319" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A320" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>325</v>
-      </c>
-      <c r="B323" t="s">
-        <v>99</v>
+        <v>313</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>326</v>
-      </c>
-      <c r="B324" t="s">
-        <v>99</v>
+        <v>314</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>328</v>
+        <v>316</v>
+      </c>
+      <c r="B326" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>332</v>
-      </c>
-      <c r="B330" t="s">
-        <v>107</v>
+        <v>425</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A344" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A345" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A346" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A347" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A348" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A349" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A337" t="s">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A352" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A338" t="s">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A353" t="s">
         <v>340</v>
       </c>
-      <c r="B338" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A339" t="s">
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A354" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A340" t="s">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A355" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A356" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A341" t="s">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A357" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A342" t="s">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A358" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A359" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A343" t="s">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A360" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A344" t="s">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A361" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A345" t="s">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A362" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A346" t="s">
+      <c r="B362" t="s">
+        <v>99</v>
+      </c>
+      <c r="C362" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A363" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A347" t="s">
+      <c r="B363" t="s">
+        <v>99</v>
+      </c>
+      <c r="C363" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A364" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A348" t="s">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A365" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A349" t="s">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A366" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A350" t="s">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A367" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A351" t="s">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A368" t="s">
         <v>353</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A352" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A353" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A354" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A355" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A356" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A357" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A358" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A359" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A360" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A361" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A362" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A363" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A364" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A365" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A366" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A367" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A368" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>375</v>
+        <v>410</v>
+      </c>
+      <c r="B373" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>381</v>
-      </c>
-      <c r="B379" t="s">
-        <v>99</v>
+        <v>363</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>382</v>
-      </c>
-      <c r="B380" t="s">
-        <v>99</v>
+        <v>364</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>385</v>
+        <v>411</v>
+      </c>
+      <c r="B383" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>392</v>
-      </c>
-      <c r="B390" t="s">
-        <v>107</v>
+        <v>412</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>393</v>
-      </c>
-      <c r="B391" t="s">
-        <v>107</v>
+        <v>373</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>395</v>
+        <v>414</v>
+      </c>
+      <c r="B393" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>403</v>
-      </c>
-      <c r="B401" t="s">
-        <v>107</v>
+        <v>381</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>404</v>
-      </c>
-      <c r="B402" t="s">
-        <v>107</v>
+        <v>382</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>412</v>
+        <v>389</v>
+      </c>
+      <c r="B410" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>416</v>
-      </c>
-      <c r="B414" t="s">
-        <v>107</v>
+        <v>392</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>417</v>
       </c>
-      <c r="B415" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>423</v>
+        <v>396</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>424</v>
+        <v>397</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>425</v>
+        <v>398</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>428</v>
+        <v>400</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>431</v>
+        <v>403</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A433" t="s">
-        <v>435</v>
-      </c>
-      <c r="B433" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A434" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A435" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A436" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A437" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A438" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A439" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A440" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A441" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A442" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A443" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A444" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A445" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A446" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A447" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A448" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A449" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A450" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A451" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A452" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A453" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A454" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A455" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A456" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A457" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A458" t="s">
-        <v>460</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/data/metabolomics/metabolite_manual_annotations.xlsx
+++ b/data/metabolomics/metabolite_manual_annotations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tacaro/Documents/GitHub/DroughtSIP/data/metabolomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5346A57D-BF70-8443-9C4E-7492D902EF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEE36F6-F088-984A-B7D4-228AD9751E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{A4A94BAB-C50F-CF46-BBED-298BF0D81361}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" xr2:uid="{A4A94BAB-C50F-CF46-BBED-298BF0D81361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="438">
   <si>
     <t>compound</t>
   </si>
@@ -3681,12 +3681,6 @@
       <c r="A362" t="s">
         <v>347</v>
       </c>
-      <c r="B362" t="s">
-        <v>99</v>
-      </c>
-      <c r="C362" t="s">
-        <v>409</v>
-      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
